--- a/worklog/v2.2.3/s10/v4/finance/test/ods_finance_project_fund.xlsx
+++ b/worklog/v2.2.3/s10/v4/finance/test/ods_finance_project_fund.xlsx
@@ -1,37 +1,334 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="23040" windowHeight="9300"/>
   </bookViews>
   <sheets>
-    <sheet name="项目经费表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="项目经费表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+  <si>
+    <t>行号</t>
+  </si>
+  <si>
+    <t>项目编号</t>
+  </si>
+  <si>
+    <t>研制周期</t>
+  </si>
+  <si>
+    <t>总经费(万元)</t>
+  </si>
+  <si>
+    <t>是否重大项目</t>
+  </si>
+  <si>
+    <t>研究室</t>
+  </si>
+  <si>
+    <t>项目状态</t>
+  </si>
+  <si>
+    <t>直接成本控制数(万元)</t>
+  </si>
+  <si>
+    <t>预留间接费用和收益(万元)</t>
+  </si>
+  <si>
+    <t>直接成本账面支出总额(万元)</t>
+  </si>
+  <si>
+    <t>直接成本执行率(%)</t>
+  </si>
+  <si>
+    <t>间接费用支出和收益总额(万元)</t>
+  </si>
+  <si>
+    <t>已收款(万元)</t>
+  </si>
+  <si>
+    <t>待收经费(万元)</t>
+  </si>
+  <si>
+    <t>XM-2025-A01</t>
+  </si>
+  <si>
+    <t>2025.01-2026.12</t>
+  </si>
+  <si>
+    <t>总体室</t>
+  </si>
+  <si>
+    <t>在研</t>
+  </si>
+  <si>
+    <t>XM-2025-A02</t>
+  </si>
+  <si>
+    <t>2025.03-2026.06</t>
+  </si>
+  <si>
+    <t>动力室</t>
+  </si>
+  <si>
+    <t>XM-2025-A03</t>
+  </si>
+  <si>
+    <t>2025.06-2027.05</t>
+  </si>
+  <si>
+    <t>控制室</t>
+  </si>
+  <si>
+    <t>XM-2025-A04</t>
+  </si>
+  <si>
+    <t>2025.09-2026.12</t>
+  </si>
+  <si>
+    <t>结构室</t>
+  </si>
+  <si>
+    <t>已完成待收款</t>
+  </si>
+  <si>
+    <t>XM-2026-B01</t>
+  </si>
+  <si>
+    <t>2026.01-2027.12</t>
+  </si>
+  <si>
+    <t>制导室</t>
+  </si>
+  <si>
+    <t>XM-2026-B02</t>
+  </si>
+  <si>
+    <t>2026.02-2027.09</t>
+  </si>
+  <si>
+    <t>电子室</t>
+  </si>
+  <si>
+    <t>XM-2026-B03</t>
+  </si>
+  <si>
+    <t>2026.04-2027.06</t>
+  </si>
+  <si>
+    <t>电源室</t>
+  </si>
+  <si>
+    <t>支出待处理</t>
+  </si>
+  <si>
+    <t>XM-2026-B04</t>
+  </si>
+  <si>
+    <t>2026.06-2028.03</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
-    <fill>
-      <patternFill/>
+  <fills count="34">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -42,8 +339,194 @@
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -51,88 +534,315 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -415,524 +1125,428 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>行号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>项目编号</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>研制周期</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>总经费(万元)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>是否重大项目</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>研究室</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>项目状态</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>直接成本控制数(万元)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>预留间接费用和收益(万元)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>直接成本账面支出总额(万元)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>直接成本执行率(%)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>间接费用支出和收益总额(万元)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>已收款(万元)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>待收经费(万元)</t>
-        </is>
+    <row r="1" ht="17.65" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:14">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>XM-2025-A01</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2025.01-2026.12</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2">
         <v>5800</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>总体室</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>在研</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2">
         <v>4200</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>1200</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>3582.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>85.3</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>980</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>3200</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>2600</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:14">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>XM-2025-A02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2025.03-2026.06</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
         <v>3200</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>动力室</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>在研</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3">
         <v>2400</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>600</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>1740</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>72.5</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>420</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>1800</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>1400</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:14">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XM-2025-A03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2025.06-2027.05</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4">
         <v>4500</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>控制室</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>在研</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4">
         <v>3300</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>900</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>1980</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>60</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>510</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>2500</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>2000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:14">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>XM-2025-A04</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2025.09-2026.12</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5">
         <v>2100</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>结构室</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已完成待收款</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5">
         <v>1600</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>400</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>1523.2</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>95.2</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>380</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>1200</v>
       </c>
-      <c r="N5" t="n">
-        <v>900</v>
+      <c r="N5">
+        <v>-900</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:14">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>XM-2026-B01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026.01-2027.12</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6">
         <v>6400</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>制导室</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>在研</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6">
         <v>4800</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>1300</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>2054.4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>42.8</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>580</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>2800</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>3600</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:14">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>XM-2026-B02</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026.02-2027.09</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7">
         <v>3800</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>电子室</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>在研</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7">
         <v>2900</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>700</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>1032.4</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>35.6</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>210</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>1500</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>2300</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:14">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>XM-2026-B03</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026.04-2027.06</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8">
         <v>2600</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>电源室</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>支出待处理</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8">
         <v>2000</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>500</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>570</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>28.5</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>150</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>1000</v>
       </c>
-      <c r="N8" t="n">
-        <v>1600</v>
+      <c r="N8">
+        <v>-1600</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:14">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>XM-2026-B04</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026.06-2028.03</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9">
         <v>5200</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>结构室</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>在研</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9">
         <v>3900</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>1100</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>600.6</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>15.4</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>120</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>2000</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>3200</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>